--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-notes-du-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4909,7 +4909,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>175</v>
       </c>
@@ -4924,13 +4924,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5012,7 +5012,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>179</v>
       </c>
@@ -5027,13 +5027,13 @@
         <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5321,7 +5321,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>193</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
